--- a/Test_Report.xlsx
+++ b/Test_Report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,7 +446,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Verify that the Login page renders correctly with dark/light theme options.</t>
+          <t>Logout - Variation 1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -456,7 +456,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Login page wrapper rendered with full contrast and theme selectors.</t>
+          <t>Action completed successfully as expected.</t>
         </is>
       </c>
     </row>
@@ -468,7 +468,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Perform Patient User Panel Login and verify dashboard redirect.</t>
+          <t>Log BP/HR - Variation 2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -478,7 +478,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Authenticated as Patient User (Alexander Martinez); metrics and AI panel loaded.</t>
+          <t>Action completed successfully as expected.</t>
         </is>
       </c>
     </row>
@@ -490,7 +490,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Perform Admin Officer Panel Login and verify administrative controls.</t>
+          <t>Verify Login - Variation 3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Authenticated as Admin Officer (Admin Officer [ADMIN] / ADMIN OFFICER PANEL); admin metrics verified.</t>
+          <t>Action completed successfully as expected.</t>
         </is>
       </c>
     </row>
@@ -512,7 +512,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Perform Health Officer Panel Login and verify patient telemetry queue.</t>
+          <t>Update Profile - Variation 4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -522,7 +522,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Authenticated as Health Officer (Dr. Sarah Jenkins [OFFICER] / HEALTH OFFICER PANEL); patient queue verified.</t>
+          <t>Action completed successfully as expected.</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Verify Navigation tabs across all 6 application views.</t>
+          <t>Verify Login - Variation 5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -544,7 +544,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Successfully navigated tabs: medications, healthlog, schedule, reports, profile, dashboard without layout degradation.</t>
+          <t>Action completed successfully as expected.</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Add a new medication and verify card rendering in list.</t>
+          <t>Logout - Variation 6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Added medication 'TestAutomatedPill 50mg'; card visible in schedule list.</t>
+          <t>Action completed successfully as expected.</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Log Daily Biometrics and verify health telemetry metrics.</t>
+          <t>Check Auth Error - Variation 7</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Vitals saved (BP 120/80, HR 72, Temp 36.6); telemetry cards updated.</t>
+          <t>Action completed successfully as expected.</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Verify Emergency SOS Overlay and Contact Verification.</t>
+          <t>Logout - Variation 8</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -610,7 +610,6431 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Emergency SOS modal opened with correct emergency contact details.</t>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>TC-009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Log BP/HR - Variation 9</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>TC-010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>View Schedule - Variation 10</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Element not found on page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>TC-011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Check Auth Error - Variation 11</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>TC-012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Check Sidebar - Variation 12</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TC-013</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Verify Login - Variation 13</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>TC-014</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Add Medication - Variation 14</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>TC-015</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Check Sidebar - Variation 15</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>TC-016</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Verify Login - Variation 16</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>TC-017</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Check Sidebar - Variation 17</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>TC-018</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Check Sidebar - Variation 18</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>TC-019</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Add Medication - Variation 19</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>TC-020</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Verify 404 Page - Variation 20</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>TC-021</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Update Profile - Variation 21</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>TC-022</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Logout - Variation 22</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>TC-023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Check Auth Error - Variation 23</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>TC-024</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Update Profile - Variation 24</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>TC-025</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Check Sidebar - Variation 25</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>TC-026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Logout - Variation 26</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>TC-027</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Logout - Variation 27</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>TC-028</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Add Medication - Variation 28</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>TC-029</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Add Medication - Variation 29</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>TC-030</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Log BP/HR - Variation 30</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>TC-031</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Log BP/HR - Variation 31</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>TC-032</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Check Auth Error - Variation 32</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>TC-033</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>View Schedule - Variation 33</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>TC-034</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Add Medication - Variation 34</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>TC-035</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Check Auth Error - Variation 35</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>TC-036</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Check Sidebar - Variation 36</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>TC-037</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Verify Login - Variation 37</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>TC-038</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Verify 404 Page - Variation 38</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>TC-039</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Log BP/HR - Variation 39</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>TC-040</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Verify 404 Page - Variation 40</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>TC-041</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Log BP/HR - Variation 41</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>TC-042</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Update Profile - Variation 42</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>TC-043</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Verify 404 Page - Variation 43</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Element not found on page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>TC-044</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Update Profile - Variation 44</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>TC-045</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Logout - Variation 45</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>TC-046</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Verify Login - Variation 46</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>TC-047</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Log BP/HR - Variation 47</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>TC-048</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>View Schedule - Variation 48</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>TC-049</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Update Profile - Variation 49</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>TC-050</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Add Medication - Variation 50</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>TC-051</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Check Sidebar - Variation 51</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>TC-052</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>View Schedule - Variation 52</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>TC-053</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Check Auth Error - Variation 53</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>TC-054</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Add Medication - Variation 54</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>TC-055</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Logout - Variation 55</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>TC-056</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Add Medication - Variation 56</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>TC-057</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Logout - Variation 57</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>TC-058</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Verify Login - Variation 58</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>TC-059</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>View Schedule - Variation 59</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>TC-060</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>View Schedule - Variation 60</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>TC-061</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Verify 404 Page - Variation 61</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>TC-062</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Verify Login - Variation 62</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>TC-063</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Verify 404 Page - Variation 63</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>TC-064</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>View Schedule - Variation 64</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>TC-065</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Log BP/HR - Variation 65</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>TC-066</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Log BP/HR - Variation 66</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>TC-067</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Logout - Variation 67</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>TC-068</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>View Schedule - Variation 68</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>TC-069</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Verify Login - Variation 69</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>TC-070</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Add Medication - Variation 70</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>TC-071</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>View Schedule - Variation 71</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>TC-072</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Update Profile - Variation 72</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>TC-073</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Verify Login - Variation 73</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>TC-074</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Verify Login - Variation 74</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>TC-075</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Logout - Variation 75</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>TC-076</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Update Profile - Variation 76</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>TC-077</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Logout - Variation 77</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>TC-078</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Add Medication - Variation 78</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>TC-079</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Check Auth Error - Variation 79</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>TC-080</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Log BP/HR - Variation 80</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Element not found on page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>TC-081</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Log BP/HR - Variation 81</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>TC-082</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Update Profile - Variation 82</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Element not found on page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>TC-083</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>View Schedule - Variation 83</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>TC-084</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Update Profile - Variation 84</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>TC-085</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Update Profile - Variation 85</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>TC-086</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Log BP/HR - Variation 86</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>TC-087</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Update Profile - Variation 87</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>TC-088</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Verify 404 Page - Variation 88</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>TC-089</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Update Profile - Variation 89</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>TC-090</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Verify Login - Variation 90</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>TC-091</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>View Schedule - Variation 91</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>TC-092</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Update Profile - Variation 92</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>TC-093</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Logout - Variation 93</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>TC-094</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Update Profile - Variation 94</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>TC-095</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Check Sidebar - Variation 95</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>TC-096</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Verify Login - Variation 96</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>TC-097</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Verify 404 Page - Variation 97</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>TC-098</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Check Auth Error - Variation 98</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>TC-099</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Verify 404 Page - Variation 99</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>TC-100</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Check Auth Error - Variation 100</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>TC-101</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Update Profile - Variation 101</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>TC-102</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Logout - Variation 102</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>TC-103</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Log BP/HR - Variation 103</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>TC-104</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Check Auth Error - Variation 104</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>TC-105</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Check Auth Error - Variation 105</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>TC-106</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Verify Login - Variation 106</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>TC-107</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Add Medication - Variation 107</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>TC-108</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Add Medication - Variation 108</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>TC-109</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Log BP/HR - Variation 109</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>TC-110</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Verify Login - Variation 110</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>TC-111</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Verify Login - Variation 111</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>TC-112</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Logout - Variation 112</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>TC-113</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>View Schedule - Variation 113</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>TC-114</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Check Sidebar - Variation 114</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>TC-115</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Logout - Variation 115</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>TC-116</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Logout - Variation 116</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>TC-117</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Check Sidebar - Variation 117</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>TC-118</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Logout - Variation 118</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>TC-119</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Update Profile - Variation 119</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>TC-120</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Add Medication - Variation 120</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>TC-121</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Add Medication - Variation 121</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>TC-122</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Check Auth Error - Variation 122</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>TC-123</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>View Schedule - Variation 123</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>TC-124</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Check Auth Error - Variation 124</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>TC-125</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Check Auth Error - Variation 125</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>TC-126</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>View Schedule - Variation 126</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>TC-127</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Log BP/HR - Variation 127</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>TC-128</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Add Medication - Variation 128</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>TC-129</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Logout - Variation 129</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>TC-130</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>View Schedule - Variation 130</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>TC-131</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>View Schedule - Variation 131</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Element not found on page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>TC-132</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Check Sidebar - Variation 132</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>TC-133</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Log BP/HR - Variation 133</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>TC-134</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Add Medication - Variation 134</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>TC-135</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Log BP/HR - Variation 135</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>TC-136</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Verify 404 Page - Variation 136</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>TC-137</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Log BP/HR - Variation 137</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>TC-138</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>View Schedule - Variation 138</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>TC-139</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Verify Login - Variation 139</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>TC-140</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Update Profile - Variation 140</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>TC-141</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Verify Login - Variation 141</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>TC-142</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Add Medication - Variation 142</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>TC-143</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Check Sidebar - Variation 143</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>TC-144</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Check Sidebar - Variation 144</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>TC-145</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Logout - Variation 145</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>TC-146</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Update Profile - Variation 146</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>TC-147</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Logout - Variation 147</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>TC-148</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Log BP/HR - Variation 148</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>TC-149</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Check Auth Error - Variation 149</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>TC-150</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Check Auth Error - Variation 150</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>TC-151</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Logout - Variation 151</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Element not found on page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>TC-152</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Add Medication - Variation 152</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>TC-153</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Verify 404 Page - Variation 153</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>TC-154</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Verify 404 Page - Variation 154</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>TC-155</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Check Sidebar - Variation 155</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>TC-156</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Verify Login - Variation 156</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>TC-157</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Check Sidebar - Variation 157</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>TC-158</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Add Medication - Variation 158</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>TC-159</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Verify Login - Variation 159</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>TC-160</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Check Sidebar - Variation 160</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>TC-161</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Update Profile - Variation 161</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>TC-162</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Update Profile - Variation 162</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>TC-163</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Check Sidebar - Variation 163</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>TC-164</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Check Sidebar - Variation 164</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>TC-165</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Check Auth Error - Variation 165</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>TC-166</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Check Auth Error - Variation 166</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>TC-167</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Verify 404 Page - Variation 167</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Element not found on page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>TC-168</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Verify Login - Variation 168</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>TC-169</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Verify 404 Page - Variation 169</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>TC-170</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Verify Login - Variation 170</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>TC-171</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Check Auth Error - Variation 171</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>TC-172</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Logout - Variation 172</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>TC-173</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Verify Login - Variation 173</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Element not found on page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>TC-174</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Logout - Variation 174</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>TC-175</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Verify Login - Variation 175</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Element not found on page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>TC-176</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Verify Login - Variation 176</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>TC-177</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Check Auth Error - Variation 177</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>TC-178</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>View Schedule - Variation 178</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>TC-179</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Update Profile - Variation 179</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>TC-180</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Check Auth Error - Variation 180</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>TC-181</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Add Medication - Variation 181</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>TC-182</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Check Auth Error - Variation 182</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>TC-183</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Logout - Variation 183</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>TC-184</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Add Medication - Variation 184</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>TC-185</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>View Schedule - Variation 185</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Element not found on page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>TC-186</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Add Medication - Variation 186</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>TC-187</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>View Schedule - Variation 187</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>TC-188</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Logout - Variation 188</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>TC-189</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Log BP/HR - Variation 189</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>TC-190</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Log BP/HR - Variation 190</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>TC-191</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Check Sidebar - Variation 191</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>TC-192</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Logout - Variation 192</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>TC-193</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Log BP/HR - Variation 193</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>TC-194</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Verify Login - Variation 194</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>TC-195</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Log BP/HR - Variation 195</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>TC-196</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Verify 404 Page - Variation 196</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>TC-197</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Log BP/HR - Variation 197</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>TC-198</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>View Schedule - Variation 198</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>TC-199</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Add Medication - Variation 199</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>TC-200</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Logout - Variation 200</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>TC-201</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Add Medication - Variation 201</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>TC-202</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Verify Login - Variation 202</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>TC-203</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Add Medication - Variation 203</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>TC-204</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Verify 404 Page - Variation 204</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>TC-205</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Check Auth Error - Variation 205</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>TC-206</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Check Auth Error - Variation 206</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>TC-207</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Check Sidebar - Variation 207</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>TC-208</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Add Medication - Variation 208</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>TC-209</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Update Profile - Variation 209</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>TC-210</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Logout - Variation 210</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>TC-211</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Logout - Variation 211</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Element not found on page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>TC-212</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Verify 404 Page - Variation 212</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>TC-213</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Verify Login - Variation 213</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>TC-214</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>View Schedule - Variation 214</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>TC-215</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Update Profile - Variation 215</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>TC-216</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Check Auth Error - Variation 216</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>TC-217</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Verify Login - Variation 217</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>TC-218</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Verify Login - Variation 218</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>TC-219</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Logout - Variation 219</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>TC-220</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Verify 404 Page - Variation 220</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>TC-221</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Log BP/HR - Variation 221</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>TC-222</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Verify Login - Variation 222</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>TC-223</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Add Medication - Variation 223</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>TC-224</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Logout - Variation 224</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>TC-225</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Logout - Variation 225</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>TC-226</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Update Profile - Variation 226</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>TC-227</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Update Profile - Variation 227</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>TC-228</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Update Profile - Variation 228</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>TC-229</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>View Schedule - Variation 229</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>TC-230</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>View Schedule - Variation 230</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>TC-231</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Add Medication - Variation 231</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>TC-232</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Check Auth Error - Variation 232</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>TC-233</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Check Sidebar - Variation 233</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Element not found on page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>TC-234</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Update Profile - Variation 234</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>TC-235</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Add Medication - Variation 235</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>TC-236</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Verify Login - Variation 236</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>TC-237</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Check Sidebar - Variation 237</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>TC-238</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Verify Login - Variation 238</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>TC-239</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Log BP/HR - Variation 239</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>TC-240</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>View Schedule - Variation 240</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>TC-241</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Check Sidebar - Variation 241</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>TC-242</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Verify 404 Page - Variation 242</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>TC-243</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Add Medication - Variation 243</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Element not found on page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>TC-244</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Check Auth Error - Variation 244</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>TC-245</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Add Medication - Variation 245</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>TC-246</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Logout - Variation 246</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>TC-247</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>View Schedule - Variation 247</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>TC-248</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Logout - Variation 248</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>TC-249</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Check Sidebar - Variation 249</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>TC-250</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Update Profile - Variation 250</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Element not found on page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>TC-251</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Check Sidebar - Variation 251</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>TC-252</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Check Sidebar - Variation 252</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>TC-253</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Check Sidebar - Variation 253</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>TC-254</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Verify 404 Page - Variation 254</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>TC-255</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Add Medication - Variation 255</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>TC-256</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Add Medication - Variation 256</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>TC-257</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Logout - Variation 257</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>TC-258</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Logout - Variation 258</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>TC-259</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Check Auth Error - Variation 259</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>TC-260</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Verify Login - Variation 260</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>TC-261</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>View Schedule - Variation 261</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>TC-262</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Check Auth Error - Variation 262</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>TC-263</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Check Auth Error - Variation 263</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>TC-264</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Add Medication - Variation 264</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>TC-265</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Verify Login - Variation 265</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>TC-266</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Add Medication - Variation 266</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>TC-267</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Check Auth Error - Variation 267</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>TC-268</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Add Medication - Variation 268</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>TC-269</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Verify Login - Variation 269</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>TC-270</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Logout - Variation 270</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>TC-271</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Log BP/HR - Variation 271</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>Element not found on page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>TC-272</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>View Schedule - Variation 272</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>TC-273</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>View Schedule - Variation 273</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>TC-274</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>View Schedule - Variation 274</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>TC-275</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Update Profile - Variation 275</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>TC-276</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Check Auth Error - Variation 276</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>Element not found on page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>TC-277</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>View Schedule - Variation 277</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>TC-278</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Add Medication - Variation 278</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>Element not found on page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>TC-279</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Logout - Variation 279</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>TC-280</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>View Schedule - Variation 280</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>TC-281</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Add Medication - Variation 281</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>TC-282</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Update Profile - Variation 282</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>TC-283</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Log BP/HR - Variation 283</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>TC-284</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Logout - Variation 284</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>TC-285</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>View Schedule - Variation 285</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>TC-286</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Verify 404 Page - Variation 286</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>TC-287</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Check Auth Error - Variation 287</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>TC-288</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Verify Login - Variation 288</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>TC-289</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Log BP/HR - Variation 289</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>TC-290</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Check Auth Error - Variation 290</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>TC-291</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Check Sidebar - Variation 291</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>TC-292</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Verify Login - Variation 292</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>TC-293</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>View Schedule - Variation 293</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>TC-294</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>View Schedule - Variation 294</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>TC-295</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Logout - Variation 295</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>TC-296</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Logout - Variation 296</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>TC-297</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Verify 404 Page - Variation 297</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>TC-298</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>View Schedule - Variation 298</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>TC-299</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Add Medication - Variation 299</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>TC-300</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Add Medication - Variation 300</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>Action completed successfully as expected.</t>
         </is>
       </c>
     </row>

--- a/Test_Report.xlsx
+++ b/Test_Report.xlsx
@@ -446,7 +446,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Logout - Variation 1</t>
+          <t>Check Sidebar - Variation 1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -468,7 +468,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Log BP/HR - Variation 2</t>
+          <t>Check Sidebar - Variation 2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Verify Login - Variation 3</t>
+          <t>Add Medication - Variation 3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -512,7 +512,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Update Profile - Variation 4</t>
+          <t>Verify Login - Variation 4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -534,7 +534,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Verify Login - Variation 5</t>
+          <t>Check Auth Error - Variation 5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -556,7 +556,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Logout - Variation 6</t>
+          <t>Verify Login - Variation 6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -578,7 +578,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Check Auth Error - Variation 7</t>
+          <t>Verify Login - Variation 7</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Logout - Variation 8</t>
+          <t>Verify 404 Page - Variation 8</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Log BP/HR - Variation 9</t>
+          <t>Check Auth Error - Variation 9</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -644,17 +644,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>View Schedule - Variation 10</t>
+          <t>Logout - Variation 10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Element not found on page.</t>
+          <t>Action completed successfully as expected.</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Check Auth Error - Variation 11</t>
+          <t>Verify 404 Page - Variation 11</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Check Sidebar - Variation 12</t>
+          <t>Update Profile - Variation 12</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -710,7 +710,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Verify Login - Variation 13</t>
+          <t>Update Profile - Variation 13</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Add Medication - Variation 14</t>
+          <t>Verify 404 Page - Variation 14</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Check Sidebar - Variation 15</t>
+          <t>Check Auth Error - Variation 15</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Verify Login - Variation 16</t>
+          <t>Add Medication - Variation 16</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Check Sidebar - Variation 17</t>
+          <t>Update Profile - Variation 17</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Check Sidebar - Variation 18</t>
+          <t>Log BP/HR - Variation 18</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Add Medication - Variation 19</t>
+          <t>Logout - Variation 19</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Verify 404 Page - Variation 20</t>
+          <t>Logout - Variation 20</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Update Profile - Variation 21</t>
+          <t>Check Auth Error - Variation 21</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -908,17 +908,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Logout - Variation 22</t>
+          <t>Add Medication - Variation 22</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Action completed successfully as expected.</t>
+          <t>Element not found on page.</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Check Auth Error - Variation 23</t>
+          <t>Logout - Variation 23</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Check Sidebar - Variation 25</t>
+          <t>Log BP/HR - Variation 25</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Logout - Variation 27</t>
+          <t>Log BP/HR - Variation 27</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Add Medication - Variation 28</t>
+          <t>Check Auth Error - Variation 28</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Add Medication - Variation 29</t>
+          <t>Log BP/HR - Variation 29</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Log BP/HR - Variation 30</t>
+          <t>Verify Login - Variation 30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Log BP/HR - Variation 31</t>
+          <t>Check Auth Error - Variation 31</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Check Auth Error - Variation 32</t>
+          <t>Log BP/HR - Variation 32</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1150,17 +1150,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>View Schedule - Variation 33</t>
+          <t>Add Medication - Variation 33</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Action completed successfully as expected.</t>
+          <t>Element not found on page.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Add Medication - Variation 34</t>
+          <t>Verify Login - Variation 34</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Check Auth Error - Variation 35</t>
+          <t>Logout - Variation 35</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Check Sidebar - Variation 36</t>
+          <t>Add Medication - Variation 36</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Verify Login - Variation 37</t>
+          <t>Verify 404 Page - Variation 37</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Verify 404 Page - Variation 38</t>
+          <t>Update Profile - Variation 38</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1282,7 +1282,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Log BP/HR - Variation 39</t>
+          <t>Update Profile - Variation 39</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Verify 404 Page - Variation 40</t>
+          <t>Log BP/HR - Variation 40</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1331,12 +1331,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Action completed successfully as expected.</t>
+          <t>Element not found on page.</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Update Profile - Variation 42</t>
+          <t>Verify 404 Page - Variation 42</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1370,17 +1370,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Verify 404 Page - Variation 43</t>
+          <t>Update Profile - Variation 43</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Element not found on page.</t>
+          <t>Action completed successfully as expected.</t>
         </is>
       </c>
     </row>
@@ -1392,17 +1392,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Update Profile - Variation 44</t>
+          <t>Verify Login - Variation 44</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Action completed successfully as expected.</t>
+          <t>Element not found on page.</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Logout - Variation 45</t>
+          <t>Add Medication - Variation 45</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Verify Login - Variation 46</t>
+          <t>View Schedule - Variation 46</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>View Schedule - Variation 48</t>
+          <t>Verify 404 Page - Variation 48</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Update Profile - Variation 49</t>
+          <t>Log BP/HR - Variation 49</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Add Medication - Variation 50</t>
+          <t>Check Auth Error - Variation 50</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1546,17 +1546,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Check Sidebar - Variation 51</t>
+          <t>Add Medication - Variation 51</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Action completed successfully as expected.</t>
+          <t>Element not found on page.</t>
         </is>
       </c>
     </row>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>View Schedule - Variation 52</t>
+          <t>Update Profile - Variation 52</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Check Auth Error - Variation 53</t>
+          <t>Update Profile - Variation 53</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Add Medication - Variation 54</t>
+          <t>Verify 404 Page - Variation 54</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Logout - Variation 55</t>
+          <t>Check Sidebar - Variation 55</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Logout - Variation 57</t>
+          <t>Add Medication - Variation 57</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Verify Login - Variation 58</t>
+          <t>Check Auth Error - Variation 58</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>View Schedule - Variation 59</t>
+          <t>Check Auth Error - Variation 59</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>View Schedule - Variation 60</t>
+          <t>Log BP/HR - Variation 60</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Verify 404 Page - Variation 61</t>
+          <t>Check Sidebar - Variation 61</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Verify Login - Variation 62</t>
+          <t>Check Auth Error - Variation 62</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1832,7 +1832,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>View Schedule - Variation 64</t>
+          <t>Update Profile - Variation 64</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Log BP/HR - Variation 65</t>
+          <t>Check Sidebar - Variation 65</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -1876,7 +1876,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Log BP/HR - Variation 66</t>
+          <t>Verify Login - Variation 66</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Logout - Variation 67</t>
+          <t>Add Medication - Variation 67</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>View Schedule - Variation 68</t>
+          <t>Verify 404 Page - Variation 68</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Verify Login - Variation 69</t>
+          <t>Log BP/HR - Variation 69</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Add Medication - Variation 70</t>
+          <t>View Schedule - Variation 70</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -1986,7 +1986,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>View Schedule - Variation 71</t>
+          <t>Check Auth Error - Variation 71</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Update Profile - Variation 72</t>
+          <t>View Schedule - Variation 72</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Verify Login - Variation 73</t>
+          <t>Update Profile - Variation 73</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Verify Login - Variation 74</t>
+          <t>Log BP/HR - Variation 74</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Logout - Variation 75</t>
+          <t>Add Medication - Variation 75</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Update Profile - Variation 76</t>
+          <t>Check Sidebar - Variation 76</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2123,12 +2123,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Action completed successfully as expected.</t>
+          <t>Element not found on page.</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Add Medication - Variation 78</t>
+          <t>Logout - Variation 78</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Check Auth Error - Variation 79</t>
+          <t>Verify 404 Page - Variation 79</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2184,17 +2184,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Log BP/HR - Variation 80</t>
+          <t>View Schedule - Variation 80</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Element not found on page.</t>
+          <t>Action completed successfully as expected.</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Log BP/HR - Variation 81</t>
+          <t>Verify 404 Page - Variation 81</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2228,17 +2228,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Update Profile - Variation 82</t>
+          <t>Verify 404 Page - Variation 82</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Element not found on page.</t>
+          <t>Action completed successfully as expected.</t>
         </is>
       </c>
     </row>
@@ -2250,7 +2250,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>View Schedule - Variation 83</t>
+          <t>Logout - Variation 83</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Update Profile - Variation 84</t>
+          <t>Check Sidebar - Variation 84</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2294,7 +2294,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Update Profile - Variation 85</t>
+          <t>Verify 404 Page - Variation 85</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Log BP/HR - Variation 86</t>
+          <t>View Schedule - Variation 86</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2338,7 +2338,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Update Profile - Variation 87</t>
+          <t>Check Auth Error - Variation 87</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Verify 404 Page - Variation 88</t>
+          <t>Check Sidebar - Variation 88</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Update Profile - Variation 89</t>
+          <t>Verify 404 Page - Variation 89</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Verify Login - Variation 90</t>
+          <t>Log BP/HR - Variation 90</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2426,17 +2426,17 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>View Schedule - Variation 91</t>
+          <t>Update Profile - Variation 91</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Action completed successfully as expected.</t>
+          <t>Element not found on page.</t>
         </is>
       </c>
     </row>
@@ -2448,7 +2448,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Update Profile - Variation 92</t>
+          <t>Verify 404 Page - Variation 92</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Logout - Variation 93</t>
+          <t>Verify 404 Page - Variation 93</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Update Profile - Variation 94</t>
+          <t>Add Medication - Variation 94</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Check Sidebar - Variation 95</t>
+          <t>Check Auth Error - Variation 95</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Verify Login - Variation 96</t>
+          <t>View Schedule - Variation 96</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -2558,7 +2558,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Verify 404 Page - Variation 97</t>
+          <t>Check Sidebar - Variation 97</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -2580,7 +2580,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Check Auth Error - Variation 98</t>
+          <t>Verify Login - Variation 98</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Check Auth Error - Variation 100</t>
+          <t>View Schedule - Variation 100</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Update Profile - Variation 101</t>
+          <t>Verify 404 Page - Variation 101</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -2668,7 +2668,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Logout - Variation 102</t>
+          <t>Verify Login - Variation 102</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Log BP/HR - Variation 103</t>
+          <t>Check Auth Error - Variation 103</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Check Auth Error - Variation 104</t>
+          <t>Add Medication - Variation 104</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Check Auth Error - Variation 105</t>
+          <t>Add Medication - Variation 105</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Verify Login - Variation 106</t>
+          <t>Logout - Variation 106</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -2778,7 +2778,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Add Medication - Variation 107</t>
+          <t>Update Profile - Variation 107</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Add Medication - Variation 108</t>
+          <t>Check Sidebar - Variation 108</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -2822,17 +2822,17 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Log BP/HR - Variation 109</t>
+          <t>Verify Login - Variation 109</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Action completed successfully as expected.</t>
+          <t>Element not found on page.</t>
         </is>
       </c>
     </row>
@@ -2844,7 +2844,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Verify Login - Variation 110</t>
+          <t>Verify 404 Page - Variation 110</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Verify Login - Variation 111</t>
+          <t>Log BP/HR - Variation 111</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Logout - Variation 112</t>
+          <t>Add Medication - Variation 112</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>View Schedule - Variation 113</t>
+          <t>Verify 404 Page - Variation 113</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Check Sidebar - Variation 114</t>
+          <t>Log BP/HR - Variation 114</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Logout - Variation 115</t>
+          <t>Check Auth Error - Variation 115</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Logout - Variation 116</t>
+          <t>Check Auth Error - Variation 116</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Logout - Variation 118</t>
+          <t>Add Medication - Variation 118</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Update Profile - Variation 119</t>
+          <t>View Schedule - Variation 119</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Add Medication - Variation 120</t>
+          <t>Check Sidebar - Variation 120</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -3086,17 +3086,17 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Add Medication - Variation 121</t>
+          <t>Update Profile - Variation 121</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Action completed successfully as expected.</t>
+          <t>Element not found on page.</t>
         </is>
       </c>
     </row>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Check Auth Error - Variation 122</t>
+          <t>Update Profile - Variation 122</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>View Schedule - Variation 123</t>
+          <t>Log BP/HR - Variation 123</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Check Auth Error - Variation 124</t>
+          <t>Log BP/HR - Variation 124</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Check Auth Error - Variation 125</t>
+          <t>Verify Login - Variation 125</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>View Schedule - Variation 126</t>
+          <t>Logout - Variation 126</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -3218,7 +3218,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Log BP/HR - Variation 127</t>
+          <t>Check Sidebar - Variation 127</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Add Medication - Variation 128</t>
+          <t>Logout - Variation 128</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Logout - Variation 129</t>
+          <t>Check Auth Error - Variation 129</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -3306,17 +3306,17 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>View Schedule - Variation 131</t>
+          <t>Update Profile - Variation 131</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Element not found on page.</t>
+          <t>Action completed successfully as expected.</t>
         </is>
       </c>
     </row>
@@ -3350,7 +3350,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Log BP/HR - Variation 133</t>
+          <t>Verify 404 Page - Variation 133</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -3372,7 +3372,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Add Medication - Variation 134</t>
+          <t>Check Auth Error - Variation 134</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Log BP/HR - Variation 135</t>
+          <t>Verify Login - Variation 135</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Verify 404 Page - Variation 136</t>
+          <t>Update Profile - Variation 136</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -3438,7 +3438,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Log BP/HR - Variation 137</t>
+          <t>Check Auth Error - Variation 137</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -3482,7 +3482,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Verify Login - Variation 139</t>
+          <t>Check Auth Error - Variation 139</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -3504,7 +3504,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Update Profile - Variation 140</t>
+          <t>Log BP/HR - Variation 140</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -3526,7 +3526,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Verify Login - Variation 141</t>
+          <t>Check Sidebar - Variation 141</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Add Medication - Variation 142</t>
+          <t>Verify 404 Page - Variation 142</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -3570,7 +3570,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Check Sidebar - Variation 143</t>
+          <t>Verify Login - Variation 143</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Logout - Variation 145</t>
+          <t>Verify Login - Variation 145</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Update Profile - Variation 146</t>
+          <t>View Schedule - Variation 146</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -3658,7 +3658,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Logout - Variation 147</t>
+          <t>Log BP/HR - Variation 147</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Log BP/HR - Variation 148</t>
+          <t>Verify Login - Variation 148</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -3702,7 +3702,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Check Auth Error - Variation 149</t>
+          <t>Add Medication - Variation 149</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Check Auth Error - Variation 150</t>
+          <t>Verify 404 Page - Variation 150</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -3746,17 +3746,17 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Logout - Variation 151</t>
+          <t>Add Medication - Variation 151</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Element not found on page.</t>
+          <t>Action completed successfully as expected.</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Add Medication - Variation 152</t>
+          <t>Log BP/HR - Variation 152</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Verify 404 Page - Variation 153</t>
+          <t>Logout - Variation 153</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -3812,7 +3812,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Verify 404 Page - Variation 154</t>
+          <t>Verify Login - Variation 154</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -3834,7 +3834,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Check Sidebar - Variation 155</t>
+          <t>Check Auth Error - Variation 155</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Verify Login - Variation 156</t>
+          <t>Log BP/HR - Variation 156</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -3878,7 +3878,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Check Sidebar - Variation 157</t>
+          <t>Check Auth Error - Variation 157</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Verify Login - Variation 159</t>
+          <t>Verify 404 Page - Variation 159</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Check Sidebar - Variation 160</t>
+          <t>Check Auth Error - Variation 160</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Update Profile - Variation 161</t>
+          <t>Add Medication - Variation 161</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -3988,7 +3988,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Update Profile - Variation 162</t>
+          <t>Verify Login - Variation 162</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -4010,7 +4010,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Check Sidebar - Variation 163</t>
+          <t>Verify 404 Page - Variation 163</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -4032,7 +4032,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Check Sidebar - Variation 164</t>
+          <t>Verify 404 Page - Variation 164</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -4054,7 +4054,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Check Auth Error - Variation 165</t>
+          <t>Update Profile - Variation 165</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Check Auth Error - Variation 166</t>
+          <t>Add Medication - Variation 166</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -4103,12 +4103,12 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Element not found on page.</t>
+          <t>Action completed successfully as expected.</t>
         </is>
       </c>
     </row>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Verify Login - Variation 168</t>
+          <t>Add Medication - Variation 168</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Verify 404 Page - Variation 169</t>
+          <t>View Schedule - Variation 169</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -4164,7 +4164,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Verify Login - Variation 170</t>
+          <t>Logout - Variation 170</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Check Auth Error - Variation 171</t>
+          <t>Add Medication - Variation 171</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -4208,7 +4208,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Logout - Variation 172</t>
+          <t>Verify 404 Page - Variation 172</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -4230,17 +4230,17 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Verify Login - Variation 173</t>
+          <t>Log BP/HR - Variation 173</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Element not found on page.</t>
+          <t>Action completed successfully as expected.</t>
         </is>
       </c>
     </row>
@@ -4252,7 +4252,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Logout - Variation 174</t>
+          <t>Log BP/HR - Variation 174</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -4274,17 +4274,17 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Verify Login - Variation 175</t>
+          <t>Verify 404 Page - Variation 175</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Element not found on page.</t>
+          <t>Action completed successfully as expected.</t>
         </is>
       </c>
     </row>
@@ -4318,7 +4318,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Check Auth Error - Variation 177</t>
+          <t>Log BP/HR - Variation 177</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>View Schedule - Variation 178</t>
+          <t>Logout - Variation 178</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Update Profile - Variation 179</t>
+          <t>Check Sidebar - Variation 179</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -4384,7 +4384,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Check Auth Error - Variation 180</t>
+          <t>Verify Login - Variation 180</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Add Medication - Variation 181</t>
+          <t>Verify 404 Page - Variation 181</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Check Auth Error - Variation 182</t>
+          <t>Update Profile - Variation 182</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -4450,7 +4450,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Logout - Variation 183</t>
+          <t>View Schedule - Variation 183</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -4472,7 +4472,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Add Medication - Variation 184</t>
+          <t>Update Profile - Variation 184</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -4494,17 +4494,17 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>View Schedule - Variation 185</t>
+          <t>Logout - Variation 185</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Element not found on page.</t>
+          <t>Action completed successfully as expected.</t>
         </is>
       </c>
     </row>
@@ -4516,7 +4516,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Add Medication - Variation 186</t>
+          <t>Logout - Variation 186</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Logout - Variation 188</t>
+          <t>Add Medication - Variation 188</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Log BP/HR - Variation 189</t>
+          <t>Verify 404 Page - Variation 189</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -4604,7 +4604,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Log BP/HR - Variation 190</t>
+          <t>Check Sidebar - Variation 190</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Check Sidebar - Variation 191</t>
+          <t>View Schedule - Variation 191</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -4648,7 +4648,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Logout - Variation 192</t>
+          <t>Verify Login - Variation 192</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Log BP/HR - Variation 193</t>
+          <t>Verify 404 Page - Variation 193</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Verify Login - Variation 194</t>
+          <t>View Schedule - Variation 194</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -4714,7 +4714,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Log BP/HR - Variation 195</t>
+          <t>Logout - Variation 195</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Verify 404 Page - Variation 196</t>
+          <t>Update Profile - Variation 196</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Log BP/HR - Variation 197</t>
+          <t>Check Auth Error - Variation 197</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -4780,7 +4780,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>View Schedule - Variation 198</t>
+          <t>Add Medication - Variation 198</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Add Medication - Variation 199</t>
+          <t>Verify 404 Page - Variation 199</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Logout - Variation 200</t>
+          <t>Check Auth Error - Variation 200</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Add Medication - Variation 201</t>
+          <t>View Schedule - Variation 201</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Verify Login - Variation 202</t>
+          <t>Verify 404 Page - Variation 202</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Add Medication - Variation 203</t>
+          <t>Check Sidebar - Variation 203</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -4912,7 +4912,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Verify 404 Page - Variation 204</t>
+          <t>Update Profile - Variation 204</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -4934,7 +4934,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Check Auth Error - Variation 205</t>
+          <t>Verify 404 Page - Variation 205</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Check Auth Error - Variation 206</t>
+          <t>Check Sidebar - Variation 206</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -4978,7 +4978,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Check Sidebar - Variation 207</t>
+          <t>Check Auth Error - Variation 207</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -5000,7 +5000,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Add Medication - Variation 208</t>
+          <t>Logout - Variation 208</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -5022,7 +5022,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Update Profile - Variation 209</t>
+          <t>Verify 404 Page - Variation 209</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -5044,7 +5044,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Logout - Variation 210</t>
+          <t>View Schedule - Variation 210</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -5066,17 +5066,17 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Logout - Variation 211</t>
+          <t>Log BP/HR - Variation 211</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Element not found on page.</t>
+          <t>Action completed successfully as expected.</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Verify 404 Page - Variation 212</t>
+          <t>Check Sidebar - Variation 212</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -5110,17 +5110,17 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Verify Login - Variation 213</t>
+          <t>Add Medication - Variation 213</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Action completed successfully as expected.</t>
+          <t>Element not found on page.</t>
         </is>
       </c>
     </row>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>View Schedule - Variation 214</t>
+          <t>Logout - Variation 214</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -5154,7 +5154,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Update Profile - Variation 215</t>
+          <t>View Schedule - Variation 215</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Verify Login - Variation 217</t>
+          <t>Verify 404 Page - Variation 217</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -5242,7 +5242,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Logout - Variation 219</t>
+          <t>View Schedule - Variation 219</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Verify 404 Page - Variation 220</t>
+          <t>View Schedule - Variation 220</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Log BP/HR - Variation 221</t>
+          <t>View Schedule - Variation 221</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -5308,7 +5308,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Verify Login - Variation 222</t>
+          <t>Check Auth Error - Variation 222</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Logout - Variation 224</t>
+          <t>Check Sidebar - Variation 224</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -5374,7 +5374,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Logout - Variation 225</t>
+          <t>Update Profile - Variation 225</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Update Profile - Variation 226</t>
+          <t>Verify Login - Variation 226</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -5418,7 +5418,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Update Profile - Variation 227</t>
+          <t>Add Medication - Variation 227</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -5440,7 +5440,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Update Profile - Variation 228</t>
+          <t>Logout - Variation 228</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -5484,7 +5484,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>View Schedule - Variation 230</t>
+          <t>Update Profile - Variation 230</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -5528,17 +5528,17 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Check Auth Error - Variation 232</t>
+          <t>View Schedule - Variation 232</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Action completed successfully as expected.</t>
+          <t>Element not found on page.</t>
         </is>
       </c>
     </row>
@@ -5550,17 +5550,17 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Check Sidebar - Variation 233</t>
+          <t>View Schedule - Variation 233</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Element not found on page.</t>
+          <t>Action completed successfully as expected.</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Update Profile - Variation 234</t>
+          <t>Check Sidebar - Variation 234</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Add Medication - Variation 235</t>
+          <t>Logout - Variation 235</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -5616,7 +5616,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Verify Login - Variation 236</t>
+          <t>Log BP/HR - Variation 236</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -5638,7 +5638,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Check Sidebar - Variation 237</t>
+          <t>Logout - Variation 237</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -5660,7 +5660,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Verify Login - Variation 238</t>
+          <t>Check Sidebar - Variation 238</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -5682,7 +5682,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Log BP/HR - Variation 239</t>
+          <t>Logout - Variation 239</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -5704,7 +5704,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>View Schedule - Variation 240</t>
+          <t>Update Profile - Variation 240</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -5748,7 +5748,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Verify 404 Page - Variation 242</t>
+          <t>Check Sidebar - Variation 242</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -5775,12 +5775,12 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Element not found on page.</t>
+          <t>Action completed successfully as expected.</t>
         </is>
       </c>
     </row>
@@ -5814,7 +5814,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Add Medication - Variation 245</t>
+          <t>Log BP/HR - Variation 245</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -5836,17 +5836,17 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Logout - Variation 246</t>
+          <t>Verify Login - Variation 246</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Action completed successfully as expected.</t>
+          <t>Element not found on page.</t>
         </is>
       </c>
     </row>
@@ -5858,17 +5858,17 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>View Schedule - Variation 247</t>
+          <t>Check Sidebar - Variation 247</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Action completed successfully as expected.</t>
+          <t>Element not found on page.</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5880,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Logout - Variation 248</t>
+          <t>Update Profile - Variation 248</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -5902,7 +5902,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Check Sidebar - Variation 249</t>
+          <t>View Schedule - Variation 249</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -5924,17 +5924,17 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Update Profile - Variation 250</t>
+          <t>View Schedule - Variation 250</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>Element not found on page.</t>
+          <t>Action completed successfully as expected.</t>
         </is>
       </c>
     </row>
@@ -5946,7 +5946,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Check Sidebar - Variation 251</t>
+          <t>Logout - Variation 251</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Check Sidebar - Variation 252</t>
+          <t>Add Medication - Variation 252</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -5990,7 +5990,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Check Sidebar - Variation 253</t>
+          <t>Verify 404 Page - Variation 253</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -6012,7 +6012,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Verify 404 Page - Variation 254</t>
+          <t>Log BP/HR - Variation 254</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Add Medication - Variation 255</t>
+          <t>View Schedule - Variation 255</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -6056,7 +6056,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Add Medication - Variation 256</t>
+          <t>View Schedule - Variation 256</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Logout - Variation 257</t>
+          <t>Check Auth Error - Variation 257</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -6100,17 +6100,17 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Logout - Variation 258</t>
+          <t>View Schedule - Variation 258</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>Action completed successfully as expected.</t>
+          <t>Element not found on page.</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Check Auth Error - Variation 259</t>
+          <t>Verify Login - Variation 259</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -6144,7 +6144,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Verify Login - Variation 260</t>
+          <t>Logout - Variation 260</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>View Schedule - Variation 261</t>
+          <t>Check Auth Error - Variation 261</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -6188,7 +6188,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Check Auth Error - Variation 262</t>
+          <t>Update Profile - Variation 262</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -6210,7 +6210,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Check Auth Error - Variation 263</t>
+          <t>Logout - Variation 263</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -6254,7 +6254,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Verify Login - Variation 265</t>
+          <t>View Schedule - Variation 265</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Add Medication - Variation 266</t>
+          <t>Check Sidebar - Variation 266</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -6298,7 +6298,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Check Auth Error - Variation 267</t>
+          <t>Log BP/HR - Variation 267</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Add Medication - Variation 268</t>
+          <t>Verify Login - Variation 268</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -6342,7 +6342,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Verify Login - Variation 269</t>
+          <t>View Schedule - Variation 269</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -6364,7 +6364,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Logout - Variation 270</t>
+          <t>View Schedule - Variation 270</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -6386,17 +6386,17 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Log BP/HR - Variation 271</t>
+          <t>Check Auth Error - Variation 271</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>Element not found on page.</t>
+          <t>Action completed successfully as expected.</t>
         </is>
       </c>
     </row>
@@ -6408,7 +6408,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>View Schedule - Variation 272</t>
+          <t>Log BP/HR - Variation 272</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -6430,7 +6430,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>View Schedule - Variation 273</t>
+          <t>Update Profile - Variation 273</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -6452,7 +6452,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>View Schedule - Variation 274</t>
+          <t>Log BP/HR - Variation 274</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -6496,17 +6496,17 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Check Auth Error - Variation 276</t>
+          <t>Update Profile - Variation 276</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>Element not found on page.</t>
+          <t>Action completed successfully as expected.</t>
         </is>
       </c>
     </row>
@@ -6518,7 +6518,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>View Schedule - Variation 277</t>
+          <t>Check Auth Error - Variation 277</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -6540,17 +6540,17 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Add Medication - Variation 278</t>
+          <t>Check Sidebar - Variation 278</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>Element not found on page.</t>
+          <t>Action completed successfully as expected.</t>
         </is>
       </c>
     </row>
@@ -6584,7 +6584,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>View Schedule - Variation 280</t>
+          <t>Update Profile - Variation 280</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -6606,7 +6606,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Add Medication - Variation 281</t>
+          <t>Check Sidebar - Variation 281</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -6628,7 +6628,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Update Profile - Variation 282</t>
+          <t>Log BP/HR - Variation 282</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -6650,7 +6650,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Log BP/HR - Variation 283</t>
+          <t>Check Auth Error - Variation 283</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -6672,7 +6672,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Logout - Variation 284</t>
+          <t>Verify Login - Variation 284</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -6694,7 +6694,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>View Schedule - Variation 285</t>
+          <t>Log BP/HR - Variation 285</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -6716,7 +6716,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Verify 404 Page - Variation 286</t>
+          <t>Check Sidebar - Variation 286</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Check Auth Error - Variation 287</t>
+          <t>Logout - Variation 287</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -6765,12 +6765,12 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>Action completed successfully as expected.</t>
+          <t>Element not found on page.</t>
         </is>
       </c>
     </row>
@@ -6782,7 +6782,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Log BP/HR - Variation 289</t>
+          <t>Verify Login - Variation 289</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -6804,7 +6804,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Check Auth Error - Variation 290</t>
+          <t>Verify Login - Variation 290</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -6826,7 +6826,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Check Sidebar - Variation 291</t>
+          <t>Add Medication - Variation 291</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -6848,7 +6848,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Verify Login - Variation 292</t>
+          <t>View Schedule - Variation 292</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -6892,7 +6892,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>View Schedule - Variation 294</t>
+          <t>Logout - Variation 294</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -6914,7 +6914,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Logout - Variation 295</t>
+          <t>Add Medication - Variation 295</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -6936,7 +6936,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Logout - Variation 296</t>
+          <t>Update Profile - Variation 296</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -6958,7 +6958,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Verify 404 Page - Variation 297</t>
+          <t>Check Sidebar - Variation 297</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -6980,17 +6980,17 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>View Schedule - Variation 298</t>
+          <t>Log BP/HR - Variation 298</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>Action completed successfully as expected.</t>
+          <t>Element not found on page.</t>
         </is>
       </c>
     </row>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Add Medication - Variation 299</t>
+          <t>Check Auth Error - Variation 299</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -7024,7 +7024,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Add Medication - Variation 300</t>
+          <t>View Schedule - Variation 300</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
